--- a/inputs/bra/bra_v01_lookups.xlsx
+++ b/inputs/bra/bra_v01_lookups.xlsx
@@ -4141,7 +4141,7 @@
     <t xml:space="preserve">producao</t>
   </si>
   <si>
-    <t xml:space="preserve">Supply</t>
+    <t xml:space="preserve">t01</t>
   </si>
   <si>
     <t xml:space="preserve">C6:BS135</t>
@@ -4180,7 +4180,7 @@
     <t xml:space="preserve">CI</t>
   </si>
   <si>
-    <t xml:space="preserve">Use</t>
+    <t xml:space="preserve">t02</t>
   </si>
   <si>
     <t xml:space="preserve">q05</t>
@@ -4201,7 +4201,7 @@
     <t xml:space="preserve">VA</t>
   </si>
   <si>
-    <t xml:space="preserve">Value Added</t>
+    <t xml:space="preserve">t03</t>
   </si>
   <si>
     <t xml:space="preserve">B6:BR6</t>
